--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB0F1BA-E56C-47C4-A3CC-ED3B3B07D486}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D145DF6E-0C46-46FA-9720-64135EF3C5A8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="14">
   <si>
     <t>Wk</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Researching group project requirements, getting familiar with project documentation, writing agenda</t>
+  </si>
+  <si>
+    <t>11:00AM</t>
+  </si>
+  <si>
+    <t>Team meeting</t>
   </si>
 </sst>
 </file>
@@ -303,6 +309,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -313,6 +323,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -335,24 +353,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -438,6 +444,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -770,7 +780,7 @@
     <col min="3" max="3" width="8.1796875" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="58.6328125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" style="1"/>
     <col min="9" max="9" width="7.7265625" style="1" customWidth="1"/>
@@ -778,41 +788,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
+      <c r="A3" s="10"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -825,9 +835,9 @@
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -836,7 +846,7 @@
       <c r="B4" s="4">
         <v>44770</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="4">
@@ -862,21 +872,33 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4">
+        <v>44770</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4">
+        <v>44770</v>
+      </c>
       <c r="E5" s="5"/>
-      <c r="G5" s="6" t="str">
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="6" t="e">
         <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v xml:space="preserve"> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="H5" s="1" t="e">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="1" t="e">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -1330,24 +1352,24 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="15" t="s">
+      <c r="A31" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="12"/>
+      <c r="D31" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="7" t="s">
+      <c r="E31" s="12"/>
+      <c r="F31" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I31" s="1" t="e">
@@ -1356,7 +1378,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
+      <c r="A32" s="10"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -1369,9 +1391,9 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
       <c r="I32" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
@@ -1939,24 +1961,24 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="15" t="s">
+      <c r="A65" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="12"/>
+      <c r="D65" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="7" t="s">
+      <c r="E65" s="12"/>
+      <c r="F65" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G65" s="7" t="s">
+      <c r="G65" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="H65" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I65" s="1" t="e">
@@ -1965,7 +1987,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A66" s="9"/>
+      <c r="A66" s="10"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
       </c>
@@ -1978,9 +2000,9 @@
       <c r="E66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
       <c r="I66" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
@@ -2435,24 +2457,24 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="15" t="s">
+      <c r="A99" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="12"/>
+      <c r="D99" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
-      <c r="F99" s="7" t="s">
+      <c r="E99" s="12"/>
+      <c r="F99" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G99" s="7" t="s">
+      <c r="G99" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H99" s="7" t="s">
+      <c r="H99" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I99" s="1" t="e">
@@ -2461,7 +2483,7 @@
       </c>
     </row>
     <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A100" s="9"/>
+      <c r="A100" s="10"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
       </c>
@@ -2474,9 +2496,9 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
       <c r="I100" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
@@ -2932,18 +2954,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -2957,6 +2967,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D145DF6E-0C46-46FA-9720-64135EF3C5A8}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ED2E167-1226-49A0-BEE7-84D84FBB1580}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="11">
   <si>
     <t>Wk</t>
   </si>
@@ -63,8 +63,14 @@
 Hours</t>
   </si>
   <si>
+    <t>Researching group project requirements, getting familiar with project documentation, writing agenda</t>
+  </si>
+  <si>
+    <t>Team meeting</t>
+  </si>
+  <si>
     <r>
-      <t>CITS3200 Project Billed Hours Record for Christo Wesseloo</t>
+      <t>CITS3200 Project Billed Hours Record for &lt;Christo Wesseloo&gt;</t>
     </r>
     <r>
       <rPr>
@@ -75,21 +81,6 @@
       <t xml:space="preserve">
 Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
     </r>
-  </si>
-  <si>
-    <t>08:30AM</t>
-  </si>
-  <si>
-    <t>09:45AM</t>
-  </si>
-  <si>
-    <t>Researching group project requirements, getting familiar with project documentation, writing agenda</t>
-  </si>
-  <si>
-    <t>11:00AM</t>
-  </si>
-  <si>
-    <t>Team meeting</t>
   </si>
 </sst>
 </file>
@@ -284,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -309,10 +300,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -323,14 +310,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -351,6 +330,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -444,10 +431,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -776,53 +759,53 @@
   <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="58.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" style="1"/>
-    <col min="9" max="9" width="7.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
     <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="15"/>
+      <c r="A1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -835,9 +818,9 @@
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="17"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -846,29 +829,29 @@
       <c r="B4" s="4">
         <v>44770</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
+      <c r="C4" s="5">
+        <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="4">
         <v>44770</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
+      <c r="E4" s="5">
+        <v>0.40625</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="e">
+        <v>8</v>
+      </c>
+      <c r="G4" s="6">
         <f>IF(I4&gt;0,I4,IF(I4=0, " ", "ERROR"))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H4" s="1" t="e">
+        <v>1.2500000000582077</v>
+      </c>
+      <c r="H4" s="1">
         <f>IF(G4&lt;&gt;"ERROR",G4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I4" s="1" t="e">
+        <v>1.2500000000582077</v>
+      </c>
+      <c r="I4" s="1">
         <f>((D4+E4)-(B4+C4))*24</f>
-        <v>#VALUE!</v>
+        <v>1.2500000000582077</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -878,27 +861,29 @@
       <c r="B5" s="4">
         <v>44770</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
+      <c r="C5" s="5">
+        <v>0.45833333333333331</v>
       </c>
       <c r="D5" s="4">
         <v>44770</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5">
+        <v>0.5</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="6" t="e">
+        <v>9</v>
+      </c>
+      <c r="G5" s="6">
         <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H5" s="1" t="e">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I5" s="1" t="e">
+        <v>2.25</v>
+      </c>
+      <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>#VALUE!</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -910,9 +895,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H6" s="1" t="e">
+      <c r="H6" s="1" t="str">
         <f t="shared" ref="H6:H30" si="2">IF(AND(G6&lt;&gt;" ",G6&lt;&gt;"ERROR",H5&lt;&gt;" ", H5&lt;&gt;"ERROR"),G6+H5," ")</f>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
@@ -928,9 +913,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H7" s="1" t="e">
+      <c r="H7" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="1"/>
@@ -946,9 +931,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H8" s="1" t="e">
+      <c r="H8" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="1"/>
@@ -964,9 +949,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H9" s="1" t="e">
+      <c r="H9" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="1"/>
@@ -982,9 +967,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H10" s="1" t="e">
+      <c r="H10" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="1"/>
@@ -1000,9 +985,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H11" s="1" t="e">
+      <c r="H11" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I11" s="1">
         <f t="shared" si="1"/>
@@ -1018,9 +1003,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H12" s="1" t="e">
+      <c r="H12" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="1"/>
@@ -1036,9 +1021,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H13" s="1" t="e">
+      <c r="H13" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="1"/>
@@ -1054,9 +1039,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H14" s="1" t="e">
+      <c r="H14" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="1"/>
@@ -1072,9 +1057,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H15" s="1" t="e">
+      <c r="H15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="1"/>
@@ -1090,9 +1075,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H16" s="1" t="e">
+      <c r="H16" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="1"/>
@@ -1108,9 +1093,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H17" s="1" t="e">
+      <c r="H17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="1"/>
@@ -1126,9 +1111,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H18" s="1" t="e">
+      <c r="H18" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
@@ -1144,9 +1129,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H19" s="1" t="e">
+      <c r="H19" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
@@ -1162,9 +1147,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H20" s="1" t="e">
+      <c r="H20" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
@@ -1180,9 +1165,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H21" s="1" t="e">
+      <c r="H21" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
@@ -1198,9 +1183,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H22" s="1" t="e">
+      <c r="H22" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
@@ -1216,9 +1201,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H23" s="1" t="e">
+      <c r="H23" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="1"/>
@@ -1234,9 +1219,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H24" s="1" t="e">
+      <c r="H24" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="1"/>
@@ -1252,9 +1237,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H25" s="1" t="e">
+      <c r="H25" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="1"/>
@@ -1270,9 +1255,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H26" s="1" t="e">
+      <c r="H26" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="1"/>
@@ -1288,9 +1273,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H27" s="1" t="e">
+      <c r="H27" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="1"/>
@@ -1306,9 +1291,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H28" s="1" t="e">
+      <c r="H28" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="1"/>
@@ -1324,9 +1309,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H29" s="1" t="e">
+      <c r="H29" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="1"/>
@@ -1342,43 +1327,43 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H30" s="1" t="e">
+      <c r="H30" s="1" t="str">
         <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="1" t="e">
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I30" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I31" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
     </row>
     <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+      <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -1391,9 +1376,9 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
       <c r="I32" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
@@ -1408,9 +1393,9 @@
         <f t="shared" ref="G33:G64" si="3">IF(I33&gt;0,I33,IF(I33=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H33" s="1" t="e">
+      <c r="H33" s="1" t="str">
         <f>IF(AND(G33&lt;&gt;" ",G33&lt;&gt;"ERROR",H30&lt;&gt;" ", H30&lt;&gt;"ERROR"),G33+H30," ")</f>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="1"/>
@@ -1426,9 +1411,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H34" s="1" t="e">
+      <c r="H34" s="1" t="str">
         <f t="shared" ref="H34:H64" si="4">IF(AND(G34&lt;&gt;" ",G34&lt;&gt;"ERROR",H33&lt;&gt;" ", H33&lt;&gt;"ERROR"),G34+H33," ")</f>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="1"/>
@@ -1444,9 +1429,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H35" s="1" t="e">
+      <c r="H35" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="1"/>
@@ -1462,9 +1447,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H36" s="1" t="e">
+      <c r="H36" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="1"/>
@@ -1480,9 +1465,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H37" s="1" t="e">
+      <c r="H37" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="1"/>
@@ -1498,9 +1483,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H38" s="1" t="e">
+      <c r="H38" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="1"/>
@@ -1516,9 +1501,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H39" s="1" t="e">
+      <c r="H39" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="1"/>
@@ -1534,9 +1519,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H40" s="1" t="e">
+      <c r="H40" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="1"/>
@@ -1552,9 +1537,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H41" s="1" t="e">
+      <c r="H41" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="1"/>
@@ -1570,9 +1555,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H42" s="1" t="e">
+      <c r="H42" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="1"/>
@@ -1588,9 +1573,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H43" s="1" t="e">
+      <c r="H43" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="1"/>
@@ -1606,9 +1591,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H44" s="1" t="e">
+      <c r="H44" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="1"/>
@@ -1624,9 +1609,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H45" s="1" t="e">
+      <c r="H45" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="1"/>
@@ -1642,9 +1627,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H46" s="1" t="e">
+      <c r="H46" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I46" s="1">
         <f t="shared" si="1"/>
@@ -1660,9 +1645,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H47" s="1" t="e">
+      <c r="H47" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I47" s="1">
         <f t="shared" si="1"/>
@@ -1678,9 +1663,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H48" s="1" t="e">
+      <c r="H48" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I48" s="1">
         <f t="shared" si="1"/>
@@ -1696,9 +1681,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H49" s="1" t="e">
+      <c r="H49" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="1"/>
@@ -1714,9 +1699,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H50" s="1" t="e">
+      <c r="H50" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="1"/>
@@ -1732,9 +1717,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H51" s="1" t="e">
+      <c r="H51" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="1"/>
@@ -1750,9 +1735,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H52" s="1" t="e">
+      <c r="H52" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I52" s="1">
         <f t="shared" si="1"/>
@@ -1768,9 +1753,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H53" s="1" t="e">
+      <c r="H53" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I53" s="1">
         <f t="shared" si="1"/>
@@ -1786,9 +1771,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H54" s="1" t="e">
+      <c r="H54" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="1"/>
@@ -1804,9 +1789,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H55" s="1" t="e">
+      <c r="H55" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="1"/>
@@ -1822,9 +1807,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H56" s="1" t="e">
+      <c r="H56" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I56" s="1">
         <f t="shared" si="1"/>
@@ -1840,9 +1825,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H57" s="1" t="e">
+      <c r="H57" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I57" s="1">
         <f t="shared" si="1"/>
@@ -1858,9 +1843,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H58" s="1" t="e">
+      <c r="H58" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I58" s="1">
         <f t="shared" si="1"/>
@@ -1876,9 +1861,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H59" s="1" t="e">
+      <c r="H59" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I59" s="1">
         <f t="shared" si="1"/>
@@ -1891,9 +1876,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H60" s="1" t="e">
+      <c r="H60" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I60" s="1">
         <f t="shared" si="1"/>
@@ -1906,9 +1891,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H61" s="1" t="e">
+      <c r="H61" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I61" s="1">
         <f t="shared" si="1"/>
@@ -1921,9 +1906,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H62" s="1" t="e">
+      <c r="H62" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I62" s="1">
         <f t="shared" si="1"/>
@@ -1936,9 +1921,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H63" s="1" t="e">
+      <c r="H63" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I63" s="1">
         <f t="shared" si="1"/>
@@ -1951,43 +1936,43 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H64" s="1" t="e">
+      <c r="H64" s="1" t="str">
         <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I64" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="1" t="e">
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I64" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E65" s="12"/>
-      <c r="F65" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I65" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A66" s="10"/>
+      <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
       </c>
@@ -2000,9 +1985,9 @@
       <c r="E66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
       <c r="I66" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
@@ -2013,9 +1998,9 @@
         <f t="shared" ref="G67:G98" si="5">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H67" s="1" t="e">
+      <c r="H67" s="1" t="str">
         <f>IF(AND(G67&lt;&gt;" ",G67&lt;&gt;"ERROR",H64&lt;&gt;" ", H64&lt;&gt;"ERROR"),G67+H64," ")</f>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I67" s="1">
         <f t="shared" si="1"/>
@@ -2027,9 +2012,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H68" s="1" t="e">
+      <c r="H68" s="1" t="str">
         <f t="shared" ref="H68:H98" si="6">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ", H67&lt;&gt;"ERROR"),G68+H67," ")</f>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I68" s="1">
         <f t="shared" si="1"/>
@@ -2041,9 +2026,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H69" s="1" t="e">
+      <c r="H69" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I69" s="1">
         <f t="shared" ref="I69:I132" si="7">((D69+E69)-(B69+C69))*24</f>
@@ -2055,9 +2040,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H70" s="1" t="e">
+      <c r="H70" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="7"/>
@@ -2069,9 +2054,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H71" s="1" t="e">
+      <c r="H71" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I71" s="1">
         <f t="shared" si="7"/>
@@ -2083,9 +2068,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H72" s="1" t="e">
+      <c r="H72" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I72" s="1">
         <f t="shared" si="7"/>
@@ -2097,9 +2082,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H73" s="1" t="e">
+      <c r="H73" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I73" s="1">
         <f t="shared" si="7"/>
@@ -2111,9 +2096,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H74" s="1" t="e">
+      <c r="H74" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I74" s="1">
         <f t="shared" si="7"/>
@@ -2125,9 +2110,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H75" s="1" t="e">
+      <c r="H75" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I75" s="1">
         <f t="shared" si="7"/>
@@ -2139,9 +2124,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H76" s="1" t="e">
+      <c r="H76" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I76" s="1">
         <f t="shared" si="7"/>
@@ -2153,9 +2138,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H77" s="1" t="e">
+      <c r="H77" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I77" s="1">
         <f t="shared" si="7"/>
@@ -2167,9 +2152,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H78" s="1" t="e">
+      <c r="H78" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I78" s="1">
         <f t="shared" si="7"/>
@@ -2181,9 +2166,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H79" s="1" t="e">
+      <c r="H79" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I79" s="1">
         <f t="shared" si="7"/>
@@ -2195,9 +2180,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H80" s="1" t="e">
+      <c r="H80" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I80" s="1">
         <f t="shared" si="7"/>
@@ -2209,9 +2194,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H81" s="1" t="e">
+      <c r="H81" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I81" s="1">
         <f t="shared" si="7"/>
@@ -2223,9 +2208,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H82" s="1" t="e">
+      <c r="H82" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I82" s="1">
         <f t="shared" si="7"/>
@@ -2237,9 +2222,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H83" s="1" t="e">
+      <c r="H83" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I83" s="1">
         <f t="shared" si="7"/>
@@ -2251,9 +2236,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H84" s="1" t="e">
+      <c r="H84" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I84" s="1">
         <f t="shared" si="7"/>
@@ -2265,9 +2250,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H85" s="1" t="e">
+      <c r="H85" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I85" s="1">
         <f t="shared" si="7"/>
@@ -2279,9 +2264,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H86" s="1" t="e">
+      <c r="H86" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I86" s="1">
         <f t="shared" si="7"/>
@@ -2293,9 +2278,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H87" s="1" t="e">
+      <c r="H87" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I87" s="1">
         <f t="shared" si="7"/>
@@ -2307,9 +2292,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H88" s="1" t="e">
+      <c r="H88" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I88" s="1">
         <f t="shared" si="7"/>
@@ -2321,9 +2306,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H89" s="1" t="e">
+      <c r="H89" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I89" s="1">
         <f t="shared" si="7"/>
@@ -2335,9 +2320,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H90" s="1" t="e">
+      <c r="H90" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I90" s="1">
         <f t="shared" si="7"/>
@@ -2349,9 +2334,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H91" s="1" t="e">
+      <c r="H91" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I91" s="1">
         <f t="shared" si="7"/>
@@ -2363,9 +2348,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H92" s="1" t="e">
+      <c r="H92" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I92" s="1">
         <f t="shared" si="7"/>
@@ -2377,9 +2362,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H93" s="1" t="e">
+      <c r="H93" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I93" s="1">
         <f t="shared" si="7"/>
@@ -2391,9 +2376,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H94" s="1" t="e">
+      <c r="H94" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I94" s="1">
         <f t="shared" si="7"/>
@@ -2405,9 +2390,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H95" s="1" t="e">
+      <c r="H95" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I95" s="1">
         <f t="shared" si="7"/>
@@ -2419,9 +2404,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H96" s="1" t="e">
+      <c r="H96" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I96" s="1">
         <f t="shared" si="7"/>
@@ -2433,9 +2418,9 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H97" s="1" t="e">
+      <c r="H97" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I97" s="1">
         <f t="shared" si="7"/>
@@ -2447,43 +2432,43 @@
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H98" s="1" t="e">
+      <c r="H98" s="1" t="str">
         <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I98" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A99" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E99" s="16"/>
+      <c r="F99" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I99" s="1" t="e">
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I98" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A99" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" s="12"/>
-      <c r="D99" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E99" s="12"/>
-      <c r="F99" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I99" s="1" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
     </row>
     <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A100" s="10"/>
+      <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
       </c>
@@ -2496,9 +2481,9 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
       <c r="I100" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
@@ -2509,9 +2494,9 @@
         <f t="shared" ref="G101:G132" si="8">IF(I101&gt;0,I101,IF(I101=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H101" s="1" t="e">
+      <c r="H101" s="1" t="str">
         <f>IF(AND(G101&lt;&gt;" ",G101&lt;&gt;"ERROR",H98&lt;&gt;" ", H98&lt;&gt;"ERROR"),G101+H98," ")</f>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I101" s="1">
         <f t="shared" si="7"/>
@@ -2523,9 +2508,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H102" s="1" t="e">
+      <c r="H102" s="1" t="str">
         <f t="shared" ref="H102:H132" si="9">IF(AND(G102&lt;&gt;" ",G102&lt;&gt;"ERROR",H101&lt;&gt;" ", H101&lt;&gt;"ERROR"),G102+H101," ")</f>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I102" s="1">
         <f t="shared" si="7"/>
@@ -2537,9 +2522,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H103" s="1" t="e">
+      <c r="H103" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I103" s="1">
         <f t="shared" si="7"/>
@@ -2551,9 +2536,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H104" s="1" t="e">
+      <c r="H104" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I104" s="1">
         <f t="shared" si="7"/>
@@ -2565,9 +2550,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H105" s="1" t="e">
+      <c r="H105" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I105" s="1">
         <f t="shared" si="7"/>
@@ -2579,9 +2564,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H106" s="1" t="e">
+      <c r="H106" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I106" s="1">
         <f t="shared" si="7"/>
@@ -2593,9 +2578,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H107" s="1" t="e">
+      <c r="H107" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I107" s="1">
         <f t="shared" si="7"/>
@@ -2607,9 +2592,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H108" s="1" t="e">
+      <c r="H108" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I108" s="1">
         <f t="shared" si="7"/>
@@ -2621,9 +2606,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H109" s="1" t="e">
+      <c r="H109" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I109" s="1">
         <f t="shared" si="7"/>
@@ -2635,9 +2620,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H110" s="1" t="e">
+      <c r="H110" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I110" s="1">
         <f t="shared" si="7"/>
@@ -2649,9 +2634,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H111" s="1" t="e">
+      <c r="H111" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I111" s="1">
         <f t="shared" si="7"/>
@@ -2663,9 +2648,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H112" s="1" t="e">
+      <c r="H112" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I112" s="1">
         <f t="shared" si="7"/>
@@ -2677,9 +2662,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H113" s="1" t="e">
+      <c r="H113" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I113" s="1">
         <f t="shared" si="7"/>
@@ -2691,9 +2676,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H114" s="1" t="e">
+      <c r="H114" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I114" s="1">
         <f t="shared" si="7"/>
@@ -2705,9 +2690,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H115" s="1" t="e">
+      <c r="H115" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I115" s="1">
         <f t="shared" si="7"/>
@@ -2719,9 +2704,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H116" s="1" t="e">
+      <c r="H116" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I116" s="1">
         <f t="shared" si="7"/>
@@ -2733,9 +2718,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H117" s="1" t="e">
+      <c r="H117" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I117" s="1">
         <f t="shared" si="7"/>
@@ -2747,9 +2732,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H118" s="1" t="e">
+      <c r="H118" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I118" s="1">
         <f t="shared" si="7"/>
@@ -2761,9 +2746,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H119" s="1" t="e">
+      <c r="H119" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I119" s="1">
         <f t="shared" si="7"/>
@@ -2775,9 +2760,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H120" s="1" t="e">
+      <c r="H120" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I120" s="1">
         <f t="shared" si="7"/>
@@ -2789,9 +2774,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H121" s="1" t="e">
+      <c r="H121" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I121" s="1">
         <f t="shared" si="7"/>
@@ -2803,9 +2788,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H122" s="1" t="e">
+      <c r="H122" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I122" s="1">
         <f t="shared" si="7"/>
@@ -2817,9 +2802,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H123" s="1" t="e">
+      <c r="H123" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I123" s="1">
         <f t="shared" si="7"/>
@@ -2831,9 +2816,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H124" s="1" t="e">
+      <c r="H124" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I124" s="1">
         <f t="shared" si="7"/>
@@ -2845,9 +2830,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H125" s="1" t="e">
+      <c r="H125" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I125" s="1">
         <f t="shared" si="7"/>
@@ -2859,9 +2844,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H126" s="1" t="e">
+      <c r="H126" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I126" s="1">
         <f t="shared" si="7"/>
@@ -2873,9 +2858,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H127" s="1" t="e">
+      <c r="H127" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I127" s="1">
         <f t="shared" si="7"/>
@@ -2887,9 +2872,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H128" s="1" t="e">
+      <c r="H128" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I128" s="1">
         <f t="shared" si="7"/>
@@ -2901,9 +2886,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H129" s="1" t="e">
+      <c r="H129" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I129" s="1">
         <f t="shared" si="7"/>
@@ -2915,9 +2900,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H130" s="1" t="e">
+      <c r="H130" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I130" s="1">
         <f t="shared" si="7"/>
@@ -2929,9 +2914,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H131" s="1" t="e">
+      <c r="H131" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I131" s="1">
         <f t="shared" si="7"/>
@@ -2943,9 +2928,9 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H132" s="1" t="e">
+      <c r="H132" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I132" s="1">
         <f t="shared" si="7"/>
@@ -2954,6 +2939,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -2967,18 +2964,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ED2E167-1226-49A0-BEE7-84D84FBB1580}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F95C330-0835-4D67-96EB-56517313C574}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3315" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -312,6 +312,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -330,14 +338,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -431,6 +431,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -756,55 +760,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" style="1"/>
-    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.6328125" style="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1"/>
+    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -820,7 +824,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -887,21 +891,32 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="G6" s="6" t="str">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4">
+        <v>44770</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D6" s="4">
+        <v>44770</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="G6" s="6">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H6" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="1">
         <f t="shared" ref="H6:H30" si="2">IF(AND(G6&lt;&gt;" ",G6&lt;&gt;"ERROR",H5&lt;&gt;" ", H5&lt;&gt;"ERROR"),G6+H5," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>3</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1336,18 +1351,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1362,7 +1377,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -1945,18 +1960,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -1971,7 +1986,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -2441,18 +2456,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -2467,7 +2482,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -2939,18 +2954,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -2964,6 +2967,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2975,7 +2990,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2987,7 +3002,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F95C330-0835-4D67-96EB-56517313C574}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C791A37-CC80-45AB-8614-BF3D518683E9}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3315" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28020" yWindow="900" windowWidth="21600" windowHeight="11235" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
   <si>
     <t>Wk</t>
   </si>
@@ -81,6 +81,12 @@
       <t xml:space="preserve">
 Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
     </r>
+  </si>
+  <si>
+    <t>Writing up team documentation as well as researching project information</t>
+  </si>
+  <si>
+    <t>Client meeting</t>
   </si>
 </sst>
 </file>
@@ -312,14 +318,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -338,6 +336,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -431,10 +437,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -775,36 +777,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -824,7 +826,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -906,6 +908,9 @@
       <c r="E6" s="5">
         <v>0.67708333333333337</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G6" s="6">
         <f t="shared" si="0"/>
         <v>0.75</v>
@@ -920,21 +925,35 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="G7" s="6" t="str">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4">
+        <v>44771</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="D7" s="4">
+        <v>44771</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H7" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H7" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>3.9999999999417923</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -1355,14 +1374,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1964,14 +1983,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2460,14 +2479,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -2954,6 +2973,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -2967,18 +2998,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C791A37-CC80-45AB-8614-BF3D518683E9}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1A04513-E903-4F09-AA11-A6EC5359DF83}"/>
   <bookViews>
-    <workbookView xWindow="-28020" yWindow="900" windowWidth="21600" windowHeight="11235" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="624" yWindow="696" windowWidth="21600" windowHeight="11232" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="14">
   <si>
     <t>Wk</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Client meeting</t>
+  </si>
+  <si>
+    <t>Finishing meeting minutes</t>
   </si>
 </sst>
 </file>
@@ -957,21 +960,35 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="G8" s="6" t="str">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4">
+        <v>44771</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D8" s="4">
+        <v>44771</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="6">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H8" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H8" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>4.5</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1A04513-E903-4F09-AA11-A6EC5359DF83}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0578D03B-2083-46EF-87C1-E8BDE6E000C8}"/>
   <bookViews>
-    <workbookView xWindow="624" yWindow="696" windowWidth="21600" windowHeight="11232" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="15">
   <si>
     <t>Wk</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Finishing meeting minutes</t>
+  </si>
+  <si>
+    <t>Filling in Team Timesheet</t>
   </si>
 </sst>
 </file>
@@ -442,6 +445,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -765,21 +772,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1"/>
-    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
@@ -791,7 +798,7 @@
       <c r="G1" s="11"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -813,7 +820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -992,21 +999,35 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="G9" s="6" t="str">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4">
+        <v>44772</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D9" s="4">
+        <v>44772</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="6">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H9" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H9" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>5.0000000000582077</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -1387,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
@@ -1413,7 +1434,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -1996,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +2043,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -2492,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
@@ -2518,7 +2539,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -3026,7 +3047,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3038,7 +3059,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0578D03B-2083-46EF-87C1-E8BDE6E000C8}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ED2E167-1226-49A0-BEE7-84D84FBB1580}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="11">
   <si>
     <t>Wk</t>
   </si>
@@ -81,18 +81,6 @@
       <t xml:space="preserve">
 Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
     </r>
-  </si>
-  <si>
-    <t>Writing up team documentation as well as researching project information</t>
-  </si>
-  <si>
-    <t>Client meeting</t>
-  </si>
-  <si>
-    <t>Finishing meeting minutes</t>
-  </si>
-  <si>
-    <t>Filling in Team Timesheet</t>
   </si>
 </sst>
 </file>
@@ -445,10 +433,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -774,10 +758,10 @@
   <dimension ref="A1:I132"/>
   <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
@@ -798,7 +782,7 @@
       <c r="G1" s="11"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -820,7 +804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -903,131 +887,75 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4">
-        <v>44770</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D6" s="4">
-        <v>44770</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="G6" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="H6" s="1">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H6" s="1" t="str">
         <f t="shared" ref="H6:H30" si="2">IF(AND(G6&lt;&gt;" ",G6&lt;&gt;"ERROR",H5&lt;&gt;" ", H5&lt;&gt;"ERROR"),G6+H5," ")</f>
-        <v>3</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4">
-        <v>44771</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.5625</v>
-      </c>
-      <c r="D7" s="4">
-        <v>44771</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="G7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.99999999994179234</v>
-      </c>
-      <c r="H7" s="1">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H7" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>3.9999999999417923</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="1"/>
-        <v>0.99999999994179234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4">
-        <v>44771</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D8" s="4">
-        <v>44771</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0.875</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="G8" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.50000000005820766</v>
-      </c>
-      <c r="H8" s="1">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H8" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="1"/>
-        <v>0.50000000005820766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4">
-        <v>44772</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D9" s="4">
-        <v>44772</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.8125</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="G9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.50000000005820766</v>
-      </c>
-      <c r="H9" s="1">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H9" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>5.0000000000582077</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="1"/>
-        <v>0.50000000005820766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
